--- a/xls/square_16_tri3_25.xlsx
+++ b/xls/square_16_tri3_25.xlsx
@@ -482,13 +482,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-1.3640261120081767</v>
+        <v>-1.3640270564840797</v>
       </c>
       <c r="J25">
-        <v>-1.1905800381339542</v>
+        <v>-1.1905805635785907</v>
       </c>
       <c r="K25">
-        <v>3.5595995886718015</v>
+        <v>3.559599644619088</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -517,13 +517,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-1.0519767595717222</v>
+        <v>-1.051976657705688</v>
       </c>
       <c r="J26">
-        <v>-0.8503638232723024</v>
+        <v>-0.8503637714255007</v>
       </c>
       <c r="K26">
-        <v>3.683852111902302</v>
+        <v>3.6838521004992395</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -552,13 +552,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.39876263413856017</v>
+        <v>-0.39876262239025795</v>
       </c>
       <c r="J27">
-        <v>-0.2758307480539195</v>
+        <v>-0.2758307421867361</v>
       </c>
       <c r="K27">
-        <v>3.729409530065802</v>
+        <v>3.7294095218108443</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -587,13 +587,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>0.000559018051516374</v>
+        <v>0.000559018066539568</v>
       </c>
       <c r="J28">
-        <v>-0.00035528015152680724</v>
+        <v>-0.0003552801453704245</v>
       </c>
       <c r="K28">
-        <v>2.9969577578916278</v>
+        <v>2.996957759203526</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -622,13 +622,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.0009870713097429528</v>
+        <v>-0.0009870713107076382</v>
       </c>
       <c r="J29">
-        <v>-0.0009313468196524793</v>
+        <v>-0.0009313468201953533</v>
       </c>
       <c r="K29">
-        <v>2.912270136968875</v>
+        <v>2.91227013702253</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -657,13 +657,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.0006631405906541088</v>
+        <v>-0.0006631405911654522</v>
       </c>
       <c r="J30">
-        <v>-0.0005024371991699073</v>
+        <v>-0.0005024371994861384</v>
       </c>
       <c r="K30">
-        <v>2.6992493778061006</v>
+        <v>2.6992493779899225</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -692,13 +692,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-0.007977171199627679</v>
+        <v>-0.007977171157482484</v>
       </c>
       <c r="J31">
-        <v>-0.005689756844572822</v>
+        <v>-0.005689756815467745</v>
       </c>
       <c r="K31">
-        <v>3.1082515137795546</v>
+        <v>3.1082515120675267</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -727,13 +727,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.0002950163476154756</v>
+        <v>-0.0002950163474751189</v>
       </c>
       <c r="J32">
-        <v>-0.00023327450855131136</v>
+        <v>-0.0002332745084697337</v>
       </c>
       <c r="K32">
-        <v>2.5503271322500427</v>
+        <v>2.550327132004471</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_25.xlsx
+++ b/xls/square_16_tri3_25.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>676</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>289</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>1.0225692669332087</v>
+      </c>
+      <c r="J23">
+        <v>-1.770670656816407</v>
+      </c>
+      <c r="K23">
+        <v>2.7670964119167993</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>676</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>289</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>625</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>3456</v>
+      </c>
+      <c r="I24">
+        <v>-2.0442706495135488</v>
+      </c>
+      <c r="J24">
+        <v>-1.8827857442234825</v>
+      </c>
+      <c r="K24">
+        <v>2.3710207713947087</v>
+      </c>
+    </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>11</v>
